--- a/光伏配储项目/电价数据/2026/兴宁站.xlsx
+++ b/光伏配储项目/电价数据/2026/兴宁站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.42307</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38452</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.79289</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.46821</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.48965</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.42992</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.43975</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.39057</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.39954</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.3859</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.37543</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.37749</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.36819</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.36613</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.36373</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.35523</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.36409</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.37225</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.3705</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.33892</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.35882</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.35542</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.38006</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.36152</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.38249</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.37779</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.38593</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.3796</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.39543</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.41219</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.3083</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.3108399999999999</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.31983</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.33184</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.34939</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32241</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.24514</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.12466</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>-0.01477</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.06609999999999999</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.06997</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.05547</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.29367</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.32846</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.5156799999999999</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.5609500000000001</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.743</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.14684</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39647</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.39126</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43415</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.44097</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.6682</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.8936000000000001</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.50375</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.21751</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.35173</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.17158</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.0454</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.31347</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.41552</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.45685</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.70912</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.76098</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.13662</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.95274</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.91247</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.80816</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.77067</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.5200199999999999</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.49097</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.47106</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.42134</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.43169</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.7338600000000001</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.9103300000000001</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.9760700000000001</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.51435</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5441</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.52177</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5219199999999999</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.50314</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40834</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.48355</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38465</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.39389</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.53059</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33904</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.40699</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.39316</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.3929</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.49408</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.44295</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.44419</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.43638</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.52266</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>1.70085</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>1.60308</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>1.56735</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.56184</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.5842999999999999</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.3859</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.36666</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.39903</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.49459</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.33814</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.25709</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.3576</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.30809</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29922</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.16937</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>-0.01055</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.39786</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.37965</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.54316</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.17938</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>-0.008880000000000001</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>-0.04466</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.30637</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.32967</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.6064400000000001</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.7742100000000001</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.80769</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.19361</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.4283</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.14516</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.86683</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.23311</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.12932</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.45417</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.20867</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.11362</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.67202</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.0071</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.93002</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.9851599999999999</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.82485</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.45559</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.45511</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43315</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44914</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33426</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35763</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33552</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5233</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.50199</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.5018899999999999</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.3741</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.45339</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.42163</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.37477</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39601</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38966</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.3682</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43926</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.45654</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33809</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.3759</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.40456</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.37318</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37363</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.36056</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36662</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35613</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.4083</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.38108</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.40324</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.40831</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.48792</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.45157</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44908</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34904</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.40106</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35586</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36711</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.3483</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.22904</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.32051</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.35975</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.803</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>-0.00676</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.33098</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.3384</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.44818</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.38848</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.43637</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.36116</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.34966</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.44535</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>1.36881</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>1.4512</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.33105</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.63026</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.6702</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.47037</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.5076000000000001</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>1.27136</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.43931</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.51046</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.63161</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.73499</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>1.57148</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>1.34497</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>1.67959</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>1.79753</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.43795</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.46225</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.40015</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.3618</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.35025</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34304</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.52495</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.5114</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.44606</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.39752</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.39644</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.40047</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.37301</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.36438</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.3968</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.39421</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36913</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.45987</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.36674</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.35364</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.37103</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.36371</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.36524</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.34126</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33868</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33557</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33887</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33429</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.35271</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.34157</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35538</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.39283</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39466</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.35402</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.38177</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34715</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39853</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.42223</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.43718</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35831</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.41804</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34206</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.35577</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.30733</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.32589</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.59973</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.30145</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.40786</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.31846</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.22109</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.19439</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.32104</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.34845</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.3671</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.30821</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.4097</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.64402</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.32654</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.3025</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31401</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34245</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>1.53888</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>1.318</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.41225</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>1.02359</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.33031</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.33535</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.45094</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1.47035</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.47855</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.5290499999999999</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.4511</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.47549</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.40449</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.6414500000000001</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>1.64819</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>1.64335</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.6379199999999999</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.7605299999999999</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.52613</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.49796</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50445</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.44983</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.42711</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.41852</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.42849</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.35691</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.37451</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.3449700000000001</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32439</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32131</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.3127799999999999</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31944</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.3225</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.33229</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.36745</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.34645</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.37964</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35758</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33865</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32656</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32715</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33008</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32012</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31866</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31551</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31762</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31892</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31511</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31723</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31086</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31223</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31678</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31548</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30906</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.3085</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.3132</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31435</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33259</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31732</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.31669</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.29371</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.30676</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.31541</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.28646</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.2865</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.30571</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.30042</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30383</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.27182</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.25788</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.03838</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.13321</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.03879999999999999</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.02683</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.02892</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.2341</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29636</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29898</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29577</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30256</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33583</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.39489</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.73287</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.69787</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.71935</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.5612999999999999</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.44174</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.7441599999999999</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.65473</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.7026399999999999</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.66443</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.50099</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.59185</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.6545700000000001</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.98599</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.4397</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.40174</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.35786</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.39258</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.57104</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.37538</v>
+      </c>
+      <c r="C122" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D122" t="n">
+        <v>1.05097</v>
+      </c>
+      <c r="E122" t="n">
+        <v>1.78488</v>
+      </c>
+      <c r="F122" t="n">
+        <v>1.57157</v>
+      </c>
+      <c r="G122" t="n">
+        <v>1.69837</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.56204</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.82256</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.55279</v>
+      </c>
+      <c r="K122" t="n">
+        <v>1.25369</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.5126499999999999</v>
+      </c>
+      <c r="M122" t="n">
+        <v>1.45696</v>
+      </c>
+      <c r="N122" t="n">
+        <v>1.05251</v>
+      </c>
+      <c r="O122" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.5426</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.54775</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.53043</v>
+      </c>
+      <c r="S122" t="n">
+        <v>1.26359</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.8635</v>
+      </c>
+      <c r="U122" t="n">
+        <v>1.12029</v>
+      </c>
+      <c r="V122" t="n">
+        <v>1.16783</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.50357</v>
+      </c>
+      <c r="X122" t="n">
+        <v>1.28892</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.53073</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.9234600000000001</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.8682000000000001</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.5474199999999999</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>1.26351</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.6349</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10156</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04282</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04575</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04489</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.29186</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.00558</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.19775</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04505</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.26294</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.14069</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04334</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04548</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04338</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.01167</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04537</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.0519</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.05008</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19974</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30453</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29281</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29224</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.35685</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.41707</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.4688</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.54375</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.50971</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.46359</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.5141699999999999</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.33417</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31053</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.69037</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.49926</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32939</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27068</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31624</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29725</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.35322</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38134</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.43055</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.46038</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41842</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41525</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.39805</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.4024</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15655</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29425</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31265</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.62203</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78572</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92038</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49455</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9141900000000001</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86286</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29619</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35361</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88746</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63159</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18705</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8697</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.61165</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33081</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03289</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5307500000000001</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79096</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.55533</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77295</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77752</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87385</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49312</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39865</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39985</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44991</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20696</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87882</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55101</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62181</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53831</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49768</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43713</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45126</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38816</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42031</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.50671</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.44664</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.44209</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.43118</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.59216</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.66501</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.47457</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.49223</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.49975</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.42346</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.40669</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.49396</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.9744700000000001</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34743</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.49675</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.5710599999999999</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.63766</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.91067</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>1.45213</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>1.16885</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.91916</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>1.5762</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.89093</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.47612</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>1.25692</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>1.50051</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.94437</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>1.00256</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87503</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.45689</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>1.2346</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.42663</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.39554</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.52311</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.60026</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.40766</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.47832</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.40047</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32089</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40649</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.43087</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.33812</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31953</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.3204</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.34808</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.60329</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.30117</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.51048</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.38492</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.37167</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29597</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.34139</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.43707</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.35625</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>1.20103</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.62141</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.66103</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.61894</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.7268300000000001</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.6090099999999999</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.54974</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.6588200000000001</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.53567</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.5335700000000001</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.52586</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.62182</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.61136</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>1.11322</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>1.13131</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>1.38912</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>1.14738</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.9545</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.92904</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.54888</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="C125" t="n">
+        <v>1.11094</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.70468</v>
+      </c>
+      <c r="E125" t="n">
+        <v>1.13439</v>
+      </c>
+      <c r="F125" t="n">
+        <v>1.05554</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.9070900000000001</v>
+      </c>
+      <c r="H125" t="n">
+        <v>1.37589</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.8318099999999999</v>
+      </c>
+      <c r="J125" t="n">
+        <v>1.04189</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.6435</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.69833</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.6265299999999999</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.59102</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.69148</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.5247999999999999</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.7004400000000001</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.63618</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.4972</v>
+      </c>
+      <c r="T125" t="n">
+        <v>1.10298</v>
+      </c>
+      <c r="U125" t="n">
+        <v>1.69808</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.70237</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.9807899999999999</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.64516</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.6985</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.73429</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.84976</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.73658</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.72999</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.54488</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.4557</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.5723400000000001</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.56311</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.551</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.62636</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.39021</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.37309</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.31116</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31169</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.10886</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.26191</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>-0.03331</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30407</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.31039</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.25734</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.27468</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.15023</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.26303</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26042</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.20385</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.31807</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29898</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.33142</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.2913</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.32089</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.32119</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.37038</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.38392</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.39578</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.52147</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.50689</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.40828</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>1.34227</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.43316</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.53862</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.31849</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.46945</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.5664</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.40354</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29624</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.26352</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.67383</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.5612200000000001</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.55764</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.56343</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.28499</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.73584</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.5335</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.63391</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.514</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.67403</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.54218</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.84601</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.5990800000000001</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>1.37565</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.5357799999999999</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.56948</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.43542</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.5386299999999999</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.66071</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.63139</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.9877</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.55962</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>1.02191</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>1.053</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>1.19237</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1.19362</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.69713</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.41767</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.92606</v>
+      </c>
+      <c r="G126" t="n">
+        <v>1.01974</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.87602</v>
+      </c>
+      <c r="I126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.6649400000000001</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.7170700000000001</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.6521399999999999</v>
+      </c>
+      <c r="N126" t="n">
+        <v>1.02957</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.6276799999999999</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.6194700000000001</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.97038</v>
+      </c>
+      <c r="R126" t="n">
+        <v>1.6808</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.61848</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.64252</v>
+      </c>
+      <c r="U126" t="n">
+        <v>1.16047</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.64097</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.5880599999999999</v>
+      </c>
+      <c r="X126" t="n">
+        <v>1.33219</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>1.49177</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.6009500000000001</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.62638</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>1.35819</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.61834</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.60872</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>1.11635</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>1.33581</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.6035</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>1.15737</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.7004400000000001</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.5585</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>1.52694</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.5024</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.99048</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.7653</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.46156</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.5884199999999999</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.397</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.51375</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.42825</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>1.39575</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.55755</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.25513</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.43488</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.21659</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.39198</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27727</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.06959</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.41651</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30439</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26884</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.26501</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.31366</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28751</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.37402</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.37497</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.35373</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.41154</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.38849</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.47228</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.55432</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.45254</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.6365499999999999</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.62418</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.87578</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.8788400000000001</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.52624</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.56284</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.52608</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.7509600000000001</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.5927899999999999</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.54512</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.89123</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.66223</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.5653400000000001</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.5511699999999999</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>1.42145</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>1.34393</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>1.40055</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>1.32811</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.81045</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>1.03756</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.8459099999999999</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.76258</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.60188</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.8126</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.5849</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.7918500000000001</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>1.42969</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.89936</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.9712999999999999</v>
+      </c>
+      <c r="F127" t="n">
+        <v>1.51759</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.5301900000000001</v>
+      </c>
+      <c r="H127" t="n">
+        <v>1.2422</v>
+      </c>
+      <c r="I127" t="n">
+        <v>1.24958</v>
+      </c>
+      <c r="J127" t="n">
+        <v>1.28693</v>
+      </c>
+      <c r="K127" t="n">
+        <v>1.23393</v>
+      </c>
+      <c r="L127" t="n">
+        <v>1.45312</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.82577</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.82086</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.82486</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.52027</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.51627</v>
+      </c>
+      <c r="R127" t="n">
+        <v>1.44181</v>
+      </c>
+      <c r="S127" t="n">
+        <v>1.44116</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.51555</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.53099</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.51164</v>
+      </c>
+      <c r="W127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="X127" t="n">
+        <v>1.2293</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>1.71943</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>1.32833</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>1.76121</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>1.65691</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.90116</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.5395</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>1.11929</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.7331</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>1.50261</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.51583</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.6027400000000001</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>1.37117</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.80302</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.91988</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.94008</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>1.389</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.77035</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.09139</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.28656</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.1559</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>-0.01277</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.00524</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.27141</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.02506</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.20294</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>-0.00949</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.25782</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.38407</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.12837</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>-0.03437</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.26626</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>-0.03486</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.72811</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.53667</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.78573</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.5908600000000001</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.81051</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.73558</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.80838</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>1.00628</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.6311100000000001</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.8770800000000001</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.6359199999999999</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>1.00273</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.80372</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.97054</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>1.45834</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>1.08392</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.99124</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>1.09937</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>1.03838</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>1.41432</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>1.38895</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>1.35459</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>1.37757</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.63871</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.6021799999999999</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.58974</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.59496</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.58853</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.84705</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.83592</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.98817</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.7882400000000001</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.6622</v>
+      </c>
+      <c r="C128" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.58372</v>
+      </c>
+      <c r="E128" t="n">
+        <v>1.50258</v>
+      </c>
+      <c r="F128" t="n">
+        <v>1.17518</v>
+      </c>
+      <c r="G128" t="n">
+        <v>1.12793</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.83713</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.90454</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.8868200000000001</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.96036</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.57464</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.56525</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.8483200000000001</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.72023</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.9388300000000001</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.8033899999999999</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.91922</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.705</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.68472</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.7192799999999999</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.6682100000000001</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.6403099999999999</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.66848</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.6403099999999999</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.67555</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>1.42421</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.85842</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.90106</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.7537200000000001</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.5957100000000001</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.66371</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.5959</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.5458500000000001</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.6066900000000001</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.61691</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.56164</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.39946</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.46775</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31535</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.3629</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.36789</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.23823</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.25937</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.18773</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.14509</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.4957</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.18253</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.3157</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.21706</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30085</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30082</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31751</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31498</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.28567</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.57512</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31287</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.33503</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.24506</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.49757</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.5468099999999999</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>1.17312</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.68288</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.59978</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>1.34353</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.6216</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.7691699999999999</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.57897</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.54322</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.69699</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.63228</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.62187</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.53552</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.52723</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.6183999999999999</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.74083</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>1.52107</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.70717</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.41073</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.8530800000000001</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.47335</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.6455</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.6025499999999999</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.6921900000000001</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.68723</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.98403</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.5242899999999999</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.55277</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.67344</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.69968</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.62585</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.98538</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.84605</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.8733300000000001</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.64613</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.7205499999999999</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.47408</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.7450800000000001</v>
+      </c>
+      <c r="D129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.5658099999999999</v>
+      </c>
+      <c r="F129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.83227</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.67108</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.9097999999999999</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.79908</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.77759</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.6657999999999999</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.70112</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.66076</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.6776799999999999</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.5420499999999999</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.71163</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.65386</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.64742</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.53828</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.53374</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.6315</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.5350499999999999</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.53037</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.6437200000000001</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.64678</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.70465</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.9739800000000001</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.57517</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.83661</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.777</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.5355599999999999</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.63229</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.7255199999999999</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.5672999999999999</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.6367</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.33158</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.62988</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.8783200000000001</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.5738799999999999</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.71165</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.68201</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.5668099999999999</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.63964</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.67811</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.55557</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.6215900000000001</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.5616100000000001</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.71526</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.2672</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.26794</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.3431</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.59472</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>1.34947</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.40905</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.79757</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.58192</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.5605399999999999</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.58587</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.57363</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.53695</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.6926599999999999</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.5881000000000001</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.50198</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.58586</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>1.01196</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.78804</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.56241</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.5761900000000001</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.65112</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.53606</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.63454</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.34898</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.51595</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.8016599999999999</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.6747000000000001</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.58684</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.66518</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.6464099999999999</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.91544</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.58448</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.57247</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.7077899999999999</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.45227</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.69356</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.36107</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.5801900000000001</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.44068</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.61639</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.7569</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.7686900000000001</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>1.24784</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32005</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.8627999999999999</v>
+      </c>
+      <c r="D130" t="n">
+        <v>1.35835</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.60463</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.7735599999999999</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.6992</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.79731</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.96216</v>
+      </c>
+      <c r="J130" t="n">
+        <v>1.29916</v>
+      </c>
+      <c r="K130" t="n">
+        <v>1.22089</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.72087</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.76671</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.69474</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.7011799999999999</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.69343</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.67299</v>
+      </c>
+      <c r="R130" t="n">
+        <v>1.24193</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.5200900000000001</v>
+      </c>
+      <c r="T130" t="n">
+        <v>1.254</v>
+      </c>
+      <c r="U130" t="n">
+        <v>1.45567</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.8803300000000001</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.51532</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.51849</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.74707</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>1.25373</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>1.25094</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>1.20283</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>1.32221</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>1.55526</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>1.49357</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>1.24499</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.94626</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.68047</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.55116</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.57675</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.57897</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.53146</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.53977</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.9210700000000001</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.54312</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.46219</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.54349</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.6269199999999999</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.6643300000000001</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.67796</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.6736599999999999</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.51483</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.63229</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.48134</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.62574</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.48598</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.56829</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.52535</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.5282899999999999</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.5335599999999999</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.64719</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.6345299999999999</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.62118</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.67845</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.60492</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.57777</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>1.23332</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.7242499999999999</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.5430900000000001</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.51839</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.9485800000000001</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.8077799999999999</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.6480499999999999</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.62971</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.5535599999999999</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.58841</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.65454</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.6808099999999999</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>1.47562</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.68162</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>1.15443</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.5437799999999999</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.94302</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.5654</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.55732</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.96415</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.5585</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.92825</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.55865</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>1.09694</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>1.0202</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.56912</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>1.48822</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.55304</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>1.04947</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.56611</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>1.35331</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>1.56225</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.54684</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>1.10446</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.54644</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.649</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.54711</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.54612</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.54715</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.54808</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.54757</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.54677</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.80088</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.54611</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.5429700000000001</v>
+      </c>
+      <c r="L131" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.54375</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.74188</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.7699</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.7534400000000001</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.5363</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.53677</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.69455</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.9351499999999999</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.52111</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.7019099999999999</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.53631</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.7822</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.6741200000000001</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.7772100000000001</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.54177</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.67576</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.74195</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.74521</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.53304</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.73263</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.68451</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.77249</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.6533099999999999</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.71129</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.67811</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.5601499999999999</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.5570000000000001</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.5181399999999999</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.47922</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.38283</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.43284</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.43103</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.39686</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.369</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.47912</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.46238</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32937</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31829</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37048</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32498</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.33285</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.57845</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.43743</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.38089</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.4282</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.41923</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.36497</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.39069</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.4621499999999999</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.52077</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.57968</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.45219</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.50657</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.60846</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.55572</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.59529</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.5548</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.55636</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.56651</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.54667</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.6495299999999999</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.54872</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.6442899999999999</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.5555</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.56055</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.54544</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.7414400000000001</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.88735</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.7963</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.77898</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>1.07776</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.62064</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.76486</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.57253</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.8518</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>1.19425</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>1.16923</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>1.34999</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>1.05733</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.5470900000000001</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.55133</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.5558500000000001</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.53627</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.658</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32192</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.60802</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.57317</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.68699</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.5589299999999999</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.5560700000000001</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.55574</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.5589</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.55498</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.65699</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.55586</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.54972</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.55687</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.67631</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.553</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.54896</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.67506</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.55636</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.55669</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.5444199999999999</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.94149</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.5556599999999999</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.5533899999999999</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.5569500000000001</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.5569500000000001</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.84154</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.56276</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.5767599999999999</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.55345</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.55336</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.5480700000000001</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.54876</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.55479</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.55575</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.47372</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.57866</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.56143</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.7774800000000001</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.25168</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.04246</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28086</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.34348</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.01326</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.27416</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.29098</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.29355</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.2091</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.05956</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.1584</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.21832</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.20533</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.27341</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.25262</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.29071</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.43926</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.6764</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.26371</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29525</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.3505</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.52375</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.57565</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.59536</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.7529</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.55433</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.5989500000000001</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.35592</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.4361</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33368</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.59133</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.5654199999999999</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.93421</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32095</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>1.29889</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>1.58769</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>1.27335</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.67655</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.86778</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.8255</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.85617</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.03196</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>1.74251</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.71205</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.6240399999999999</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.6319600000000001</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>1.1871</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>1.70632</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>1.17563</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>1.0922</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.76147</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.5704400000000001</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.69926</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.66116</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34564</v>
+      </c>
+      <c r="C133" t="n">
+        <v>1.53691</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E133" t="n">
+        <v>1.72724</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G133" t="n">
+        <v>1.05061</v>
+      </c>
+      <c r="H133" t="n">
+        <v>1.06401</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.94659</v>
+      </c>
+      <c r="J133" t="n">
+        <v>1.02683</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.9779500000000001</v>
+      </c>
+      <c r="L133" t="n">
+        <v>1.05331</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.9098999999999999</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.59012</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.9136599999999999</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.90603</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.83178</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.5834900000000001</v>
+      </c>
+      <c r="S133" t="n">
+        <v>1.13149</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.9040499999999999</v>
+      </c>
+      <c r="U133" t="n">
+        <v>1.12017</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.9224199999999999</v>
+      </c>
+      <c r="W133" t="n">
+        <v>1.14062</v>
+      </c>
+      <c r="X133" t="n">
+        <v>1.03514</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>1.08199</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>1.08925</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>1.55847</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>1.4489</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>1.76131</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>1.3657</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>1.71045</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>1.34562</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.6503300000000001</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.58305</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.61129</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.63001</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.6665399999999999</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.6830499999999999</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.74776</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.63001</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.79143</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.55728</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>1.01051</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>1.09602</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.9105599999999999</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.61885</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.56625</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.5644199999999999</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.31401</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.3361</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.32718</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.40567</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.65679</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.37697</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.7139500000000001</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.31992</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.31112</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.53035</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.56813</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.99874</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.60737</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.4886</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.54448</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.5423300000000001</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.7232499999999999</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.5561200000000001</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>1.15367</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>1.08613</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>1.11204</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.9472200000000001</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>1.16196</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.8642000000000001</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>1.25015</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>1.17267</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>1.5753</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>1.35026</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>1.77288</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>1.79492</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.9635199999999999</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.81756</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.8677699999999999</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>1.6143</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>1.66478</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>1.56756</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>1.49844</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>1.4804</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>1.04181</v>
+      </c>
+      <c r="C134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D134" t="n">
+        <v>1.12854</v>
+      </c>
+      <c r="E134" t="n">
+        <v>1.23488</v>
+      </c>
+      <c r="F134" t="n">
+        <v>1.35963</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.6298400000000001</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.61979</v>
+      </c>
+      <c r="I134" t="n">
+        <v>1.29947</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.61151</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.9649800000000001</v>
+      </c>
+      <c r="L134" t="n">
+        <v>1.69626</v>
+      </c>
+      <c r="M134" t="n">
+        <v>1.12476</v>
+      </c>
+      <c r="N134" t="n">
+        <v>1.15113</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.94853</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.89842</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.7986</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.82131</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.5556</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.5524</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.56137</v>
+      </c>
+      <c r="V134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.99824</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.8613200000000001</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.55526</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.56137</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>1.11209</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>1.09457</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.57492</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.85781</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.55679</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.5505599999999999</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.5749099999999999</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.57048</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>1.1044</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.5632</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.59496</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.8732000000000001</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.58214</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35167</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.66464</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.5107200000000001</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.88348</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.9003099999999999</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>1.00359</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.6421699999999999</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.62979</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.28667</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>-0.0266</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.37367</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.36306</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.7147899999999999</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.37525</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.71114</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.41209</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.9517</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>1.28678</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.64335</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>-0.02962</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>-0.03671</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.42552</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.3238</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.59515</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.45018</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.42779</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.43774</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.8021</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.78914</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.8963099999999999</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.5861799999999999</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>1.15524</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>1.36218</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.6128899999999999</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>1.37251</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.60345</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.9386599999999999</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>1.4557</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>1.51942</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>1.51304</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>1.29084</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.89832</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>1.30901</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.57368</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>1.19457</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.55568</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.93324</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.5571499999999999</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>1.13108</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>1.68662</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.5155700000000001</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>1.60636</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>1.72978</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>1.66946</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>1.37108</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>1.25907</v>
+      </c>
+      <c r="C135" t="n">
+        <v>1.77283</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1.47282</v>
+      </c>
+      <c r="E135" t="n">
+        <v>1.30649</v>
+      </c>
+      <c r="F135" t="n">
+        <v>1.46578</v>
+      </c>
+      <c r="G135" t="n">
+        <v>1.35794</v>
+      </c>
+      <c r="H135" t="n">
+        <v>1.42879</v>
+      </c>
+      <c r="I135" t="n">
+        <v>1.55727</v>
+      </c>
+      <c r="J135" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.98478</v>
+      </c>
+      <c r="L135" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M135" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N135" t="n">
+        <v>1.55468</v>
+      </c>
+      <c r="O135" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P135" t="n">
+        <v>1.30731</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.54687</v>
+      </c>
+      <c r="R135" t="n">
+        <v>1.5563</v>
+      </c>
+      <c r="S135" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="T135" t="n">
+        <v>1.48085</v>
+      </c>
+      <c r="U135" t="n">
+        <v>1.51667</v>
+      </c>
+      <c r="V135" t="n">
+        <v>1.28919</v>
+      </c>
+      <c r="W135" t="n">
+        <v>1.49693</v>
+      </c>
+      <c r="X135" t="n">
+        <v>1.51702</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>1.53711</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>1.5572</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>1.6376</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>1.21242</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>1.42074</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.50798</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.5465099999999999</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>1.12707</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.86625</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.9828</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.76478</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.26814</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.90715</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.29197</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.30164</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.94578</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.46367</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.47943</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.32467</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.33587</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.25649</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>-0.03616</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>-0.01401</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.27656</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.36883</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.39091</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.24842</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.16798</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.7170800000000001</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.44769</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.6763899999999999</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.68925</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.89639</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.89234</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.66689</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.6320800000000001</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.73261</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.66284</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.54906</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.84734</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>1.11758</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.87849</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>1.03169</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>1.04111</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.8219</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.51035</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>1.16419</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.88991</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>1.10521</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.97648</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>1.39663</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>1.4265</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>1.39237</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>1.14502</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>1.11653</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.99386</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.9246</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>1.0918</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>1.63323</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>1.67552</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.9551000000000001</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>1.55332</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.8141799999999999</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>1.55477</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>1.1276</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.9275599999999999</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.88866</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.7436799999999999</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.75374</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.7464500000000001</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.77154</v>
+      </c>
+      <c r="H136" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I136" t="n">
+        <v>1.23274</v>
+      </c>
+      <c r="J136" t="n">
+        <v>1.21553</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.64812</v>
+      </c>
+      <c r="L136" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M136" t="n">
+        <v>1.00831</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.9023600000000001</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.93571</v>
+      </c>
+      <c r="P136" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R136" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S136" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="T136" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U136" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V136" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="W136" t="n">
+        <v>1.01195</v>
+      </c>
+      <c r="X136" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>1.18604</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.53161</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>1.6777</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.47131</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>1.78189</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.18221</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00091</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.15568</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02277</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03959</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01435</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04308</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04103</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04864</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.0483</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02445</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02947</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04963</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.03784000000000001</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04942</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00255</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.28018</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.0493</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03563</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01184</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.0353</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20778</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.27018</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.29401</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.28172</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.52385</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.47341</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.51834</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.62848</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.5502999999999999</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.54295</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.64522</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.57313</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.48846</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.72402</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.73207</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.77674</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.54647</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.54369</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.68372</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.7117</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.7908999999999999</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>1.33674</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.64644</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.83582</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.65627</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.67603</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.69192</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.7249099999999999</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.65823</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.5325599999999999</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.90324</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E137" t="n">
+        <v>1.17825</v>
+      </c>
+      <c r="F137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G137" t="n">
+        <v>1.40823</v>
+      </c>
+      <c r="H137" t="n">
+        <v>1.38602</v>
+      </c>
+      <c r="I137" t="n">
+        <v>1.68667</v>
+      </c>
+      <c r="J137" t="n">
+        <v>1.0686</v>
+      </c>
+      <c r="K137" t="n">
+        <v>1.70424</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.54627</v>
+      </c>
+      <c r="M137" t="n">
+        <v>1.5696</v>
+      </c>
+      <c r="N137" t="n">
+        <v>1.60795</v>
+      </c>
+      <c r="O137" t="n">
+        <v>1.59036</v>
+      </c>
+      <c r="P137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>1.55111</v>
+      </c>
+      <c r="R137" t="n">
+        <v>1.46978</v>
+      </c>
+      <c r="S137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="T137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="W137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="X137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.6422100000000001</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>1.78077</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.9086000000000001</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.55133</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>1.53755</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>1.08747</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.87236</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.33201</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.6088300000000001</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.03469</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.16024</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>-0.0485</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>-0.0497</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>-0.00303</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.04988</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.29886</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.32425</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30608</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>-0.04314</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.31341</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25441</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29183</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.38049</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32007</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.38031</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.5144</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.79498</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.8759400000000001</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.5969800000000001</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.7126699999999999</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.67004</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.87727</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.17539</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>1.0378</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>1.03605</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>1.04017</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>1.13662</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.64749</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.66306</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.5739500000000001</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.83609</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.83593</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>1.58385</v>
+      </c>
+      <c r="D138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.6950499999999999</v>
+      </c>
+      <c r="H138" t="n">
+        <v>1.76961</v>
+      </c>
+      <c r="I138" t="n">
+        <v>1.34635</v>
+      </c>
+      <c r="J138" t="n">
+        <v>1.42064</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.5828300000000001</v>
+      </c>
+      <c r="L138" t="n">
+        <v>1.29066</v>
+      </c>
+      <c r="M138" t="n">
+        <v>1.75893</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.95957</v>
+      </c>
+      <c r="O138" t="n">
+        <v>1.04449</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.9977699999999999</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>1.20212</v>
+      </c>
+      <c r="R138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S138" t="n">
+        <v>1.33159</v>
+      </c>
+      <c r="T138" t="n">
+        <v>1.5761</v>
+      </c>
+      <c r="U138" t="n">
+        <v>1.30442</v>
+      </c>
+      <c r="V138" t="n">
+        <v>1.53608</v>
+      </c>
+      <c r="W138" t="n">
+        <v>1.55183</v>
+      </c>
+      <c r="X138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>1.68453</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>1.49639</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>1.71788</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>1.42374</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>1.51375</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.5230900000000001</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.92825</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.60842</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.26213</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.43781</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.05368</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.42499</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.30988</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.10758</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>-0.04994</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.09289</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.24761</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.28374</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.29923</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.29112</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.30968</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.2599</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31234</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30357</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30346</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32675</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.3192</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.50012</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31868</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32571</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.3156</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.36492</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32275</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.46943</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.50007</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.3701</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.38173</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32445</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.48457</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.5075</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.49117</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.5627000000000001</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.50008</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.57862</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.37326</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.5717000000000001</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.5348099999999999</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.7031799999999999</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.72184</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.41706</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.68235</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.74527</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.6260800000000001</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>1.75646</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>1.20288</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>1.63443</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.94179</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>1.38168</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>1.35748</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>1.1202</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.76274</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.87052</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.7952899999999999</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.86791</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.82098</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.9906699999999999</v>
+      </c>
+      <c r="D139" t="n">
+        <v>1.09823</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.97603</v>
+      </c>
+      <c r="F139" t="n">
+        <v>1.02433</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.91144</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.89362</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.86125</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.71161</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.7865800000000001</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.76218</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.76285</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.55104</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.70829</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.6755399999999999</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.54659</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.76342</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.6934199999999999</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.6880700000000001</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.69775</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.6836</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.67733</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.67741</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.72866</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.6887000000000001</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.7620800000000001</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.73173</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.76283</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.6834</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.72802</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>1.45987</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.88978</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.81471</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.5999800000000001</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>1.69425</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.76171</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.63167</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.5027699999999999</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.49203</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.5595399999999999</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.5963099999999999</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.5571200000000001</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.6137</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.50935</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.37193</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.5448200000000001</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.3507</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.45431</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.30529</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.34624</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.42289</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.35381</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.3253</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32265</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.31198</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33021</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33281</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32204</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.51017</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.46531</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.6337999999999999</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.40294</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.40993</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1.01808</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.78439</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.90216</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>1.56483</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.74451</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.8289099999999999</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>1.45585</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>1.59902</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>1.63613</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.62705</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>1.14691</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>1.60306</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.8361000000000001</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.5732699999999999</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.5575</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>1.29919</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.89773</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.6675800000000001</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.8834500000000001</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.73854</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.58848</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.73811</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.72263</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.72573</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.54301</v>
+      </c>
+      <c r="C140" t="n">
+        <v>1.01927</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.83443</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.92203</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.87527</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.8226100000000001</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.66743</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.79718</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.5704900000000001</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.77616</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.7735700000000001</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.76522</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.7012200000000001</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.66108</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.66711</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.66803</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.66818</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.50662</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.71256</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.69709</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.69511</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.71665</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.54572</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.82323</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.8241900000000001</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>1.03146</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.86914</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.56168</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.6442</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.55091</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.55233</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.65584</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.58024</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39062</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.5691900000000001</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35335</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43413</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37928</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.5620299999999999</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.5471200000000001</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.55488</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31039</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36358</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.3925</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.62888</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.6194700000000001</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.5725399999999999</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29265</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.33052</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.33348</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.35181</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.32331</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.3164</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33683</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34371</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33334</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34127</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33777</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32478</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.3441</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.39058</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.67249</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.58929</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.56516</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.36963</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.61191</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.6547200000000001</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.5639400000000001</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.63439</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.61741</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.7179800000000001</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.45058</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>1.25326</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.97257</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.78813</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.9869600000000001</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.96513</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.8935599999999999</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.7986</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.80425</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.7486799999999999</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>1.07217</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>1.17356</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.93841</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.81484</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.6860299999999999</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.6844600000000001</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.68867</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.72038</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.46641</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.63675</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.56055</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.7446200000000001</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.55061</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.54057</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.77166</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.78791</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.77412</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.67974</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.54376</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.6631699999999999</v>
+      </c>
+      <c r="N141" t="n">
+        <v>1.01108</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.54373</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.5327000000000001</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.74274</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.70499</v>
+      </c>
+      <c r="S141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.7151000000000001</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.7341</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.53959</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.7912899999999999</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.53447</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.54823</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.9098200000000001</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.92323</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.57611</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.5775800000000001</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.55537</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.7196399999999999</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.7095</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.43788</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.5717300000000001</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.39161</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.45136</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.451</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.36717</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.4023</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.34233</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.23783</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.3014</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.20597</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.36145</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.34033</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.32472</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.18912</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.24465</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.03233</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.16352</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.30607</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.27611</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.02762</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>-0.01821</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.16471</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.18732</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.03258</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.05116</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.3064</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.27213</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.23064</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.24825</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.32486</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.37532</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.33073</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.42764</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.43968</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.47067</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.59435</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.5164500000000001</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.4504</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.44063</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.42606</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.5710299999999999</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.42032</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.4992</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.48808</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.73651</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.50369</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.5960800000000001</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.63644</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.5433300000000001</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.55147</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.50303</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.43592</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.46158</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.5339299999999999</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.51976</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.42462</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.59772</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.46933</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.45866</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.50318</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.47486</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.50576</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.79191</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.54186</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.5511</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.65618</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.56229</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.46565</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.51736</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.47663</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.52964</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.48347</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.47155</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.45667</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.46063</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.45661</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.49197</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.46424</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.46452</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.46139</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.45714</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.45818</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.45544</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.45544</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.44678</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.45122</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.45345</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.45032</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.44356</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.47104</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.43243</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.41412</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.43931</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.44623</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.45171</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.44648</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.42739</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.37599</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.43858</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.35663</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.39775</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.34777</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.26451</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.30289</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.28378</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.3429700000000001</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.14249</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.30143</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.29378</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.28866</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.35231</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.29181</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.23419</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.10753</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.29256</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.27351</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.42438</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.27663</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32595</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.31213</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35282</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32317</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35096</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.33254</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32898</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.37195</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.33446</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.39199</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.45575</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.45309</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.4362799999999999</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.44514</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.48087</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.40337</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.43892</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.44143</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.46946</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.43616</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.40189</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.52138</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.5682</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.46067</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.46235</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.44685</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.47796</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.5259299999999999</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.51346</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.46408</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.44956</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.42221</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.4858</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.49595</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.42019</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.4373</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.43313</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.43234</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.43709</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34871</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.5750700000000001</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.45423</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.5935</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37299</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.44607</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.44774</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.46578</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.47382</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.46506</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.46663</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.45337</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.44292</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.4247</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.49229</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.40481</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.37872</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.44281</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.46885</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.46159</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.45102</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.44814</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.43402</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.43988</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.44348</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.44359</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.39124</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.44517</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.42551</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.43197</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.34548</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.32022</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.34223</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17682</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30252</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.2892</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31324</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14645</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19967</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>-0.04898</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.23702</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>-0.04707</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>-0.04736</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.13368</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>-5.999999999999999e-05</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.03519</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.17693</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22787</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.2707</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.15778</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.24242</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.31043</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>-0.04924</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.21951</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>-0.00162</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.202</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.1513</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.26424</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.27499</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.32378</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.29125</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.31706</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.3492</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.36406</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.37702</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.4719100000000001</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.38531</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.41167</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.41744</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.40008</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.40193</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.37919</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.46926</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.56913</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.5182899999999999</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.48926</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.50573</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.4133</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.4638</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.48428</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.48252</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.45468</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.48078</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.5780700000000001</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.40116</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.46973</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.48743</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.4659</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.39764</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.44409</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.45163</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.44554</v>
       </c>
     </row>
   </sheetData>
